--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:21</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>19.3</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>106.92</v>
+        <v>106.93</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>87.62</v>
@@ -535,7 +535,7 @@
         <v>3.52</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>41.81</v>
+        <v>41.8</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>38.29</v>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:47</t>
+    <t xml:space="preserve">2026-10-05 04:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,7 +496,7 @@
         <v>106.93</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>87.62</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
         <v>3.52</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>41.8</v>
+        <v>41.81</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>38.29</v>
